--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tønsberg.xls.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tønsberg.xls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2EE9B90-B8AF-4771-9225-A9DAC15702B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{C2EE9B90-B8AF-4771-9225-A9DAC15702B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F84B01A-5B3B-4166-BBA8-9E481D44B695}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B856B024-48C7-4BFF-B5E4-3C408E652A68}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3709" uniqueCount="180">
   <si>
     <t>CAR_ID</t>
   </si>
@@ -541,6 +541,42 @@
   <si>
     <t>Tomasjord</t>
   </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>MELSOMVIK</t>
+  </si>
+  <si>
+    <t>Lebesby</t>
+  </si>
+  <si>
+    <t>Nesoddtangen</t>
+  </si>
+  <si>
+    <t>Kirkenes</t>
+  </si>
+  <si>
+    <t>Eik</t>
+  </si>
+  <si>
+    <t>Solna</t>
+  </si>
+  <si>
+    <t>Tolvsrod</t>
+  </si>
+  <si>
+    <t>Gardermoen</t>
+  </si>
+  <si>
+    <t>SIAULIAI</t>
+  </si>
+  <si>
+    <t>Tennevoll</t>
+  </si>
+  <si>
+    <t>åsgårdstrand</t>
+  </si>
 </sst>
 </file>
 
@@ -962,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA55DC7-B8AA-4BA7-B767-B74C300660C5}">
-  <dimension ref="A1:J1458"/>
+  <dimension ref="A1:J1453"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.7109375" customWidth="1"/>
@@ -29876,1246 +29912,3592 @@
       </c>
     </row>
     <row r="1112" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1112" s="1"/>
-      <c r="C1112" s="1"/>
-      <c r="D1112" s="1"/>
-      <c r="E1112" s="1"/>
-      <c r="F1112" s="1"/>
-      <c r="G1112" s="1"/>
-      <c r="H1112" s="1"/>
+      <c r="A1112" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1112" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1112" s="2">
+        <v>9851554</v>
+      </c>
+      <c r="D1112" s="2">
+        <v>7641895</v>
+      </c>
+      <c r="E1112" s="5">
+        <v>46023.958333333336</v>
+      </c>
+      <c r="F1112" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1112" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1112" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="1113" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1113" s="1"/>
-      <c r="C1113" s="1"/>
-      <c r="D1113" s="1"/>
-      <c r="E1113" s="1"/>
-      <c r="F1113" s="1"/>
-      <c r="G1113" s="1"/>
-      <c r="H1113" s="1"/>
+      <c r="A1113" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1113" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1113" s="2">
+        <v>9851888</v>
+      </c>
+      <c r="D1113" s="2">
+        <v>7649197</v>
+      </c>
+      <c r="E1113" s="5">
+        <v>46025.458333333336</v>
+      </c>
+      <c r="F1113" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1113" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1113" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1114" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1114" s="1"/>
-      <c r="C1114" s="1"/>
-      <c r="D1114" s="1"/>
-      <c r="E1114" s="1"/>
-      <c r="F1114" s="1"/>
-      <c r="G1114" s="1"/>
-      <c r="H1114" s="1"/>
+      <c r="A1114" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1114" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1114" s="2">
+        <v>9855281</v>
+      </c>
+      <c r="D1114" s="2">
+        <v>7666218</v>
+      </c>
+      <c r="E1114" s="5">
+        <v>46025.958333333336</v>
+      </c>
+      <c r="F1114" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1114" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1114" s="1" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="1115" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1115" s="1"/>
-      <c r="C1115" s="1"/>
-      <c r="D1115" s="1"/>
-      <c r="E1115" s="1"/>
-      <c r="F1115" s="1"/>
-      <c r="G1115" s="1"/>
-      <c r="H1115" s="1"/>
+      <c r="A1115" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1115" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1115" s="2">
+        <v>9854766</v>
+      </c>
+      <c r="D1115" s="2">
+        <v>6504924</v>
+      </c>
+      <c r="E1115" s="5">
+        <v>46025.958333333336</v>
+      </c>
+      <c r="F1115" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1115" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1115" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="1116" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1116" s="1"/>
-      <c r="C1116" s="1"/>
-      <c r="D1116" s="1"/>
-      <c r="E1116" s="1"/>
-      <c r="F1116" s="1"/>
-      <c r="G1116" s="1"/>
-      <c r="H1116" s="1"/>
+      <c r="A1116" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1116" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1116" s="2">
+        <v>9852088</v>
+      </c>
+      <c r="D1116" s="2">
+        <v>5743365</v>
+      </c>
+      <c r="E1116" s="5">
+        <v>46026.458333333336</v>
+      </c>
+      <c r="F1116" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1116" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1116" s="2">
+        <v>3142</v>
+      </c>
     </row>
     <row r="1117" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1117" s="1"/>
-      <c r="C1117" s="1"/>
-      <c r="D1117" s="1"/>
-      <c r="E1117" s="1"/>
-      <c r="F1117" s="1"/>
-      <c r="G1117" s="1"/>
-      <c r="H1117" s="1"/>
+      <c r="A1117" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1117" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1117" s="2">
+        <v>9858444</v>
+      </c>
+      <c r="D1117" s="2">
+        <v>6533080</v>
+      </c>
+      <c r="E1117" s="5">
+        <v>46027.458333333336</v>
+      </c>
+      <c r="F1117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1117" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1117" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="1118" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1118" s="1"/>
-      <c r="C1118" s="1"/>
-      <c r="D1118" s="1"/>
-      <c r="E1118" s="1"/>
-      <c r="F1118" s="1"/>
-      <c r="G1118" s="1"/>
-      <c r="H1118" s="1"/>
+      <c r="A1118" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1118" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1118" s="2">
+        <v>9859923</v>
+      </c>
+      <c r="D1118" s="2">
+        <v>7681645</v>
+      </c>
+      <c r="E1118" s="5">
+        <v>46028.458333333336</v>
+      </c>
+      <c r="F1118" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1118" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1118" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1119" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1119" s="1"/>
-      <c r="C1119" s="1"/>
-      <c r="D1119" s="1"/>
-      <c r="E1119" s="1"/>
-      <c r="F1119" s="1"/>
-      <c r="G1119" s="1"/>
-      <c r="H1119" s="1"/>
+      <c r="A1119" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1119" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1119" s="2">
+        <v>9860965</v>
+      </c>
+      <c r="D1119" s="2">
+        <v>7292190</v>
+      </c>
+      <c r="E1119" s="5">
+        <v>46029.458333333336</v>
+      </c>
+      <c r="F1119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1119" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1119" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1120" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1120" s="1"/>
-      <c r="C1120" s="1"/>
-      <c r="D1120" s="1"/>
-      <c r="E1120" s="1"/>
-      <c r="F1120" s="1"/>
-      <c r="G1120" s="1"/>
-      <c r="H1120" s="1"/>
+      <c r="A1120" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1120" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1120" s="2">
+        <v>9861205</v>
+      </c>
+      <c r="D1120" s="2">
+        <v>7292190</v>
+      </c>
+      <c r="E1120" s="5">
+        <v>46029.458333333336</v>
+      </c>
+      <c r="F1120" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1120" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1120" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1121" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1121" s="1"/>
-      <c r="C1121" s="1"/>
-      <c r="D1121" s="1"/>
-      <c r="E1121" s="1"/>
-      <c r="F1121" s="1"/>
-      <c r="G1121" s="1"/>
-      <c r="H1121" s="1"/>
+      <c r="A1121" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1121" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1121" s="2">
+        <v>9863410</v>
+      </c>
+      <c r="D1121" s="2">
+        <v>7235999</v>
+      </c>
+      <c r="E1121" s="5">
+        <v>46031.458333333336</v>
+      </c>
+      <c r="F1121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1121" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1121" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1122" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1122" s="1"/>
-      <c r="C1122" s="1"/>
-      <c r="D1122" s="1"/>
-      <c r="E1122" s="1"/>
-      <c r="F1122" s="1"/>
-      <c r="G1122" s="1"/>
-      <c r="H1122" s="1"/>
+      <c r="A1122" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1122" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1122" s="2">
+        <v>9864452</v>
+      </c>
+      <c r="D1122" s="2">
+        <v>6251189</v>
+      </c>
+      <c r="E1122" s="5">
+        <v>46031.458333333336</v>
+      </c>
+      <c r="F1122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1122" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1122" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="1123" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1123" s="1"/>
-      <c r="C1123" s="1"/>
-      <c r="D1123" s="1"/>
-      <c r="E1123" s="1"/>
-      <c r="F1123" s="1"/>
-      <c r="G1123" s="1"/>
-      <c r="H1123" s="1"/>
+      <c r="A1123" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1123" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1123" s="2">
+        <v>9867014</v>
+      </c>
+      <c r="D1123" s="2">
+        <v>6251189</v>
+      </c>
+      <c r="E1123" s="5">
+        <v>46032.458333333336</v>
+      </c>
+      <c r="F1123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1123" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1123" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="1124" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1124" s="1"/>
-      <c r="C1124" s="1"/>
-      <c r="D1124" s="1"/>
-      <c r="E1124" s="1"/>
-      <c r="F1124" s="1"/>
-      <c r="G1124" s="1"/>
-      <c r="H1124" s="1"/>
+      <c r="A1124" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1124" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1124" s="2">
+        <v>9856626</v>
+      </c>
+      <c r="D1124" s="2">
+        <v>4280654</v>
+      </c>
+      <c r="E1124" s="5">
+        <v>46032.958333333336</v>
+      </c>
+      <c r="F1124" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1124" s="2">
+        <v>48</v>
+      </c>
+      <c r="H1124" s="1" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="1125" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1125" s="1"/>
-      <c r="C1125" s="1"/>
-      <c r="D1125" s="1"/>
-      <c r="E1125" s="1"/>
-      <c r="F1125" s="1"/>
-      <c r="G1125" s="1"/>
-      <c r="H1125" s="1"/>
+      <c r="A1125" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1125" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1125" s="2">
+        <v>9869411</v>
+      </c>
+      <c r="D1125" s="2">
+        <v>7681468</v>
+      </c>
+      <c r="E1125" s="5">
+        <v>46033.458333333336</v>
+      </c>
+      <c r="F1125" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1125" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1125" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="1126" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1126" s="1"/>
-      <c r="C1126" s="1"/>
-      <c r="D1126" s="1"/>
-      <c r="E1126" s="1"/>
-      <c r="F1126" s="1"/>
-      <c r="G1126" s="1"/>
-      <c r="H1126" s="1"/>
+      <c r="A1126" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1126" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1126" s="2">
+        <v>9866689</v>
+      </c>
+      <c r="D1126" s="2">
+        <v>7710976</v>
+      </c>
+      <c r="E1126" s="5">
+        <v>46033.958333333336</v>
+      </c>
+      <c r="F1126" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1126" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1126" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="1127" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1127" s="1"/>
-      <c r="C1127" s="1"/>
-      <c r="D1127" s="1"/>
-      <c r="E1127" s="1"/>
-      <c r="F1127" s="1"/>
-      <c r="G1127" s="1"/>
-      <c r="H1127" s="1"/>
+      <c r="A1127" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1127" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1127" s="2">
+        <v>9866911</v>
+      </c>
+      <c r="D1127" s="2">
+        <v>7649197</v>
+      </c>
+      <c r="E1127" s="5">
+        <v>46035.458333333336</v>
+      </c>
+      <c r="F1127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1127" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1127" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1128" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1128" s="1"/>
-      <c r="C1128" s="1"/>
-      <c r="D1128" s="1"/>
-      <c r="E1128" s="1"/>
-      <c r="F1128" s="1"/>
-      <c r="G1128" s="1"/>
-      <c r="H1128" s="1"/>
+      <c r="A1128" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1128" s="2">
+        <v>9871366</v>
+      </c>
+      <c r="D1128" s="2">
+        <v>7283957</v>
+      </c>
+      <c r="E1128" s="5">
+        <v>46035.458333333336</v>
+      </c>
+      <c r="F1128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1128" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1128" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1129" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1129" s="1"/>
-      <c r="C1129" s="1"/>
-      <c r="D1129" s="1"/>
-      <c r="E1129" s="1"/>
-      <c r="F1129" s="1"/>
-      <c r="G1129" s="1"/>
-      <c r="H1129" s="1"/>
+      <c r="A1129" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1129" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1129" s="2">
+        <v>9868720</v>
+      </c>
+      <c r="D1129" s="2">
+        <v>7514006</v>
+      </c>
+      <c r="E1129" s="5">
+        <v>46036.458333333336</v>
+      </c>
+      <c r="F1129" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1129" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1129" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1130" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1130" s="1"/>
-      <c r="C1130" s="1"/>
-      <c r="D1130" s="1"/>
-      <c r="E1130" s="1"/>
-      <c r="F1130" s="1"/>
-      <c r="G1130" s="1"/>
-      <c r="H1130" s="1"/>
+      <c r="A1130" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1130" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1130" s="2">
+        <v>9874847</v>
+      </c>
+      <c r="D1130" s="2">
+        <v>7715514</v>
+      </c>
+      <c r="E1130" s="5">
+        <v>46036.958333333336</v>
+      </c>
+      <c r="F1130" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1130" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1130" s="1" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="1131" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1131" s="1"/>
-      <c r="C1131" s="1"/>
-      <c r="D1131" s="1"/>
-      <c r="E1131" s="1"/>
-      <c r="F1131" s="1"/>
-      <c r="G1131" s="1"/>
-      <c r="H1131" s="1"/>
+      <c r="A1131" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1131" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1131" s="2">
+        <v>9871218</v>
+      </c>
+      <c r="D1131" s="2">
+        <v>4200071</v>
+      </c>
+      <c r="E1131" s="5">
+        <v>46037.958333333336</v>
+      </c>
+      <c r="F1131" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1131" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1131" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1132" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1132" s="1"/>
-      <c r="C1132" s="1"/>
-      <c r="D1132" s="1"/>
-      <c r="E1132" s="1"/>
-      <c r="F1132" s="1"/>
-      <c r="G1132" s="1"/>
-      <c r="H1132" s="1"/>
+      <c r="A1132" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1132" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1132" s="2">
+        <v>9877418</v>
+      </c>
+      <c r="D1132" s="2">
+        <v>5849860</v>
+      </c>
+      <c r="E1132" s="5">
+        <v>46038.458333333336</v>
+      </c>
+      <c r="F1132" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1132" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1132" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1133" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1133" s="1"/>
-      <c r="C1133" s="1"/>
-      <c r="D1133" s="1"/>
-      <c r="E1133" s="1"/>
-      <c r="F1133" s="1"/>
-      <c r="G1133" s="1"/>
-      <c r="H1133" s="1"/>
+      <c r="A1133" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1133" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1133" s="2">
+        <v>9879914</v>
+      </c>
+      <c r="D1133" s="2">
+        <v>7367606</v>
+      </c>
+      <c r="E1133" s="5">
+        <v>46039.458333333336</v>
+      </c>
+      <c r="F1133" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1133" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1133" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1134" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1134" s="1"/>
-      <c r="C1134" s="1"/>
-      <c r="D1134" s="1"/>
-      <c r="E1134" s="1"/>
-      <c r="F1134" s="1"/>
-      <c r="G1134" s="1"/>
-      <c r="H1134" s="1"/>
+      <c r="A1134" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1134" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1134" s="2">
+        <v>9879248</v>
+      </c>
+      <c r="D1134" s="2">
+        <v>5327670</v>
+      </c>
+      <c r="E1134" s="5">
+        <v>46040.458333333336</v>
+      </c>
+      <c r="F1134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1134" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1134" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="1135" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1135" s="1"/>
-      <c r="C1135" s="1"/>
-      <c r="D1135" s="1"/>
-      <c r="E1135" s="1"/>
-      <c r="F1135" s="1"/>
-      <c r="G1135" s="1"/>
-      <c r="H1135" s="1"/>
+      <c r="A1135" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1135" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1135" s="2">
+        <v>9879960</v>
+      </c>
+      <c r="D1135" s="2">
+        <v>6504924</v>
+      </c>
+      <c r="E1135" s="5">
+        <v>46040.458333333336</v>
+      </c>
+      <c r="F1135" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1135" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1135" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="1136" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1136" s="1"/>
-      <c r="C1136" s="1"/>
-      <c r="D1136" s="1"/>
-      <c r="E1136" s="1"/>
-      <c r="F1136" s="1"/>
-      <c r="G1136" s="1"/>
-      <c r="H1136" s="1"/>
+      <c r="A1136" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1136" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1136" s="2">
+        <v>9866308</v>
+      </c>
+      <c r="D1136" s="2">
+        <v>5985917</v>
+      </c>
+      <c r="E1136" s="5">
+        <v>46040.458333333336</v>
+      </c>
+      <c r="F1136" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1136" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1136" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="1137" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1137" s="1"/>
-      <c r="C1137" s="1"/>
-      <c r="D1137" s="1"/>
-      <c r="E1137" s="1"/>
-      <c r="F1137" s="1"/>
-      <c r="G1137" s="1"/>
-      <c r="H1137" s="1"/>
+      <c r="A1137" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1137" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1137" s="2">
+        <v>9884633</v>
+      </c>
+      <c r="D1137" s="2">
+        <v>4049812</v>
+      </c>
+      <c r="E1137" s="5">
+        <v>46041.958333333336</v>
+      </c>
+      <c r="F1137" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1137" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1137" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="1138" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1138" s="1"/>
-      <c r="C1138" s="1"/>
-      <c r="D1138" s="1"/>
-      <c r="E1138" s="1"/>
-      <c r="F1138" s="1"/>
-      <c r="G1138" s="1"/>
-      <c r="H1138" s="1"/>
+      <c r="A1138" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1138" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1138" s="2">
+        <v>9867271</v>
+      </c>
+      <c r="D1138" s="2">
+        <v>7710946</v>
+      </c>
+      <c r="E1138" s="5">
+        <v>46042.458333333336</v>
+      </c>
+      <c r="F1138" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1138" s="2">
+        <v>43</v>
+      </c>
+      <c r="H1138" s="2">
+        <v>3080</v>
+      </c>
     </row>
     <row r="1139" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1139" s="1"/>
-      <c r="C1139" s="1"/>
-      <c r="D1139" s="1"/>
-      <c r="E1139" s="1"/>
-      <c r="F1139" s="1"/>
-      <c r="G1139" s="1"/>
-      <c r="H1139" s="1"/>
+      <c r="A1139" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1139" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1139" s="2">
+        <v>9888004</v>
+      </c>
+      <c r="D1139" s="2">
+        <v>6251189</v>
+      </c>
+      <c r="E1139" s="5">
+        <v>46043.458333333336</v>
+      </c>
+      <c r="F1139" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1139" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1139" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="1140" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1140" s="1"/>
-      <c r="C1140" s="1"/>
-      <c r="D1140" s="1"/>
-      <c r="E1140" s="1"/>
-      <c r="F1140" s="1"/>
-      <c r="G1140" s="1"/>
-      <c r="H1140" s="1"/>
+      <c r="A1140" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1140" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1140" s="2">
+        <v>9887040</v>
+      </c>
+      <c r="D1140" s="2">
+        <v>7053520</v>
+      </c>
+      <c r="E1140" s="5">
+        <v>46043.458333333336</v>
+      </c>
+      <c r="F1140" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1140" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1140" s="1" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="1141" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1141" s="1"/>
-      <c r="C1141" s="1"/>
-      <c r="D1141" s="1"/>
-      <c r="E1141" s="1"/>
-      <c r="F1141" s="1"/>
-      <c r="G1141" s="1"/>
-      <c r="H1141" s="1"/>
+      <c r="A1141" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1141" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1141" s="2">
+        <v>9870936</v>
+      </c>
+      <c r="D1141" s="2">
+        <v>7081246</v>
+      </c>
+      <c r="E1141" s="5">
+        <v>46044.958333333336</v>
+      </c>
+      <c r="F1141" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1141" s="2">
+        <v>37</v>
+      </c>
+      <c r="H1141" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="1142" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1142" s="1"/>
-      <c r="C1142" s="1"/>
-      <c r="D1142" s="1"/>
-      <c r="E1142" s="1"/>
-      <c r="F1142" s="1"/>
-      <c r="G1142" s="1"/>
-      <c r="H1142" s="1"/>
+      <c r="A1142" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1142" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1142" s="2">
+        <v>9890610</v>
+      </c>
+      <c r="D1142" s="2">
+        <v>4011817</v>
+      </c>
+      <c r="E1142" s="5">
+        <v>46045.458333333336</v>
+      </c>
+      <c r="F1142" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1142" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1142" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1143" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1143" s="1"/>
-      <c r="C1143" s="1"/>
-      <c r="D1143" s="1"/>
-      <c r="E1143" s="1"/>
-      <c r="F1143" s="1"/>
-      <c r="G1143" s="1"/>
-      <c r="H1143" s="1"/>
+      <c r="A1143" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1143" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1143" s="2">
+        <v>9886208</v>
+      </c>
+      <c r="D1143" s="2">
+        <v>7730711</v>
+      </c>
+      <c r="E1143" s="5">
+        <v>46045.958333333336</v>
+      </c>
+      <c r="F1143" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1143" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1143" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="1144" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1144" s="1"/>
-      <c r="C1144" s="1"/>
-      <c r="D1144" s="1"/>
-      <c r="E1144" s="1"/>
-      <c r="F1144" s="1"/>
-      <c r="G1144" s="1"/>
-      <c r="H1144" s="1"/>
+      <c r="A1144" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1144" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1144" s="2">
+        <v>9891377</v>
+      </c>
+      <c r="D1144" s="2">
+        <v>7734473</v>
+      </c>
+      <c r="E1144" s="5">
+        <v>46045.958333333336</v>
+      </c>
+      <c r="F1144" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1144" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1144" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1145" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1145" s="1"/>
-      <c r="C1145" s="1"/>
-      <c r="D1145" s="1"/>
-      <c r="E1145" s="1"/>
-      <c r="F1145" s="1"/>
-      <c r="G1145" s="1"/>
-      <c r="H1145" s="1"/>
+      <c r="A1145" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1145" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1145" s="2">
+        <v>9893269</v>
+      </c>
+      <c r="D1145" s="2">
+        <v>7039826</v>
+      </c>
+      <c r="E1145" s="5">
+        <v>46046.458333333336</v>
+      </c>
+      <c r="F1145" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1145" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1145" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1146" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1146" s="1"/>
-      <c r="C1146" s="1"/>
-      <c r="D1146" s="1"/>
-      <c r="E1146" s="1"/>
-      <c r="F1146" s="1"/>
-      <c r="G1146" s="1"/>
-      <c r="H1146" s="1"/>
+      <c r="A1146" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1146" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1146" s="2">
+        <v>9877424</v>
+      </c>
+      <c r="D1146" s="2">
+        <v>5849860</v>
+      </c>
+      <c r="E1146" s="5">
+        <v>46046.458333333336</v>
+      </c>
+      <c r="F1146" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1146" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1146" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1147" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1147" s="1"/>
-      <c r="C1147" s="1"/>
-      <c r="D1147" s="1"/>
-      <c r="E1147" s="1"/>
-      <c r="F1147" s="1"/>
-      <c r="G1147" s="1"/>
-      <c r="H1147" s="1"/>
+      <c r="A1147" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1147" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1147" s="2">
+        <v>9889934</v>
+      </c>
+      <c r="D1147" s="2">
+        <v>6765106</v>
+      </c>
+      <c r="E1147" s="5">
+        <v>46046.958333333336</v>
+      </c>
+      <c r="F1147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1147" s="2">
+        <v>52</v>
+      </c>
+      <c r="H1147" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="1148" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1148" s="1"/>
-      <c r="C1148" s="1"/>
-      <c r="D1148" s="1"/>
-      <c r="E1148" s="1"/>
-      <c r="F1148" s="1"/>
-      <c r="G1148" s="1"/>
-      <c r="H1148" s="1"/>
+      <c r="A1148" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1148" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1148" s="2">
+        <v>9894884</v>
+      </c>
+      <c r="D1148" s="2">
+        <v>7738058</v>
+      </c>
+      <c r="E1148" s="5">
+        <v>46047.458333333336</v>
+      </c>
+      <c r="F1148" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1148" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1148" s="1" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="1149" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1149" s="1"/>
-      <c r="C1149" s="1"/>
-      <c r="D1149" s="1"/>
-      <c r="E1149" s="1"/>
-      <c r="F1149" s="1"/>
-      <c r="G1149" s="1"/>
-      <c r="H1149" s="1"/>
+      <c r="A1149" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1149" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1149" s="2">
+        <v>9895166</v>
+      </c>
+      <c r="D1149" s="2">
+        <v>7734473</v>
+      </c>
+      <c r="E1149" s="5">
+        <v>46047.458333333336</v>
+      </c>
+      <c r="F1149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1149" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1149" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1150" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1150" s="1"/>
-      <c r="C1150" s="1"/>
-      <c r="D1150" s="1"/>
-      <c r="E1150" s="1"/>
-      <c r="F1150" s="1"/>
-      <c r="G1150" s="1"/>
-      <c r="H1150" s="1"/>
+      <c r="A1150" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1150" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1150" s="2">
+        <v>9892580</v>
+      </c>
+      <c r="D1150" s="2">
+        <v>7736106</v>
+      </c>
+      <c r="E1150" s="5">
+        <v>46047.958333333336</v>
+      </c>
+      <c r="F1150" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1150" s="2">
+        <v>22</v>
+      </c>
+      <c r="H1150" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1151" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1151" s="1"/>
-      <c r="C1151" s="1"/>
-      <c r="D1151" s="1"/>
-      <c r="E1151" s="1"/>
-      <c r="F1151" s="1"/>
-      <c r="G1151" s="1"/>
-      <c r="H1151" s="1"/>
+      <c r="A1151" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1151" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1151" s="2">
+        <v>9893649</v>
+      </c>
+      <c r="D1151" s="2">
+        <v>7736959</v>
+      </c>
+      <c r="E1151" s="5">
+        <v>46047.958333333336</v>
+      </c>
+      <c r="F1151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1151" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1151" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="1152" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1152" s="1"/>
-      <c r="C1152" s="1"/>
-      <c r="D1152" s="1"/>
-      <c r="E1152" s="1"/>
-      <c r="F1152" s="1"/>
-      <c r="G1152" s="1"/>
-      <c r="H1152" s="1"/>
+      <c r="A1152" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1152" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1152" s="2">
+        <v>9896116</v>
+      </c>
+      <c r="D1152" s="2">
+        <v>5591215</v>
+      </c>
+      <c r="E1152" s="5">
+        <v>46047.958333333336</v>
+      </c>
+      <c r="F1152" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1152" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1152" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="1153" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1153" s="1"/>
-      <c r="C1153" s="1"/>
-      <c r="D1153" s="1"/>
-      <c r="E1153" s="1"/>
-      <c r="F1153" s="1"/>
-      <c r="G1153" s="1"/>
-      <c r="H1153" s="1"/>
+      <c r="A1153" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1153" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1153" s="2">
+        <v>9898791</v>
+      </c>
+      <c r="D1153" s="2">
+        <v>7734473</v>
+      </c>
+      <c r="E1153" s="5">
+        <v>46049.458333333336</v>
+      </c>
+      <c r="F1153" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1153" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1153" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1154" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1154" s="1"/>
-      <c r="C1154" s="1"/>
-      <c r="D1154" s="1"/>
-      <c r="E1154" s="1"/>
-      <c r="F1154" s="1"/>
-      <c r="G1154" s="1"/>
-      <c r="H1154" s="1"/>
+      <c r="A1154" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1154" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1154" s="2">
+        <v>9899738</v>
+      </c>
+      <c r="D1154" s="2">
+        <v>4199493</v>
+      </c>
+      <c r="E1154" s="5">
+        <v>46050.458333333336</v>
+      </c>
+      <c r="F1154" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1154" s="2">
+        <v>38</v>
+      </c>
+      <c r="H1154" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="1155" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1155" s="1"/>
-      <c r="C1155" s="1"/>
-      <c r="D1155" s="1"/>
-      <c r="E1155" s="1"/>
-      <c r="F1155" s="1"/>
-      <c r="G1155" s="1"/>
-      <c r="H1155" s="1"/>
+      <c r="A1155" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1155" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1155" s="2">
+        <v>9897144</v>
+      </c>
+      <c r="D1155" s="2">
+        <v>7734473</v>
+      </c>
+      <c r="E1155" s="5">
+        <v>46050.958333333336</v>
+      </c>
+      <c r="F1155" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1155" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1155" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1156" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1156" s="1"/>
-      <c r="C1156" s="1"/>
-      <c r="D1156" s="1"/>
-      <c r="E1156" s="1"/>
-      <c r="F1156" s="1"/>
-      <c r="G1156" s="1"/>
-      <c r="H1156" s="1"/>
+      <c r="A1156" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1156" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1156" s="2">
+        <v>9811109</v>
+      </c>
+      <c r="D1156" s="2">
+        <v>3570964</v>
+      </c>
+      <c r="E1156" s="5">
+        <v>46051.958333333336</v>
+      </c>
+      <c r="F1156" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1156" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1156" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1157" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1157" s="1"/>
-      <c r="C1157" s="1"/>
-      <c r="D1157" s="1"/>
-      <c r="E1157" s="1"/>
-      <c r="F1157" s="1"/>
-      <c r="G1157" s="1"/>
-      <c r="H1157" s="1"/>
+      <c r="A1157" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1157" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1157" s="2">
+        <v>9896615</v>
+      </c>
+      <c r="D1157" s="2">
+        <v>4049812</v>
+      </c>
+      <c r="E1157" s="5">
+        <v>46052.458333333336</v>
+      </c>
+      <c r="F1157" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1157" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1157" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="1158" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1158" s="1"/>
-      <c r="C1158" s="1"/>
-      <c r="D1158" s="1"/>
-      <c r="E1158" s="1"/>
-      <c r="F1158" s="1"/>
-      <c r="G1158" s="1"/>
-      <c r="H1158" s="1"/>
+      <c r="A1158" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1158" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1158" s="2">
+        <v>9902343</v>
+      </c>
+      <c r="D1158" s="2">
+        <v>7744407</v>
+      </c>
+      <c r="E1158" s="5">
+        <v>46052.458333333336</v>
+      </c>
+      <c r="F1158" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1158" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1158" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="1159" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1159" s="1"/>
-      <c r="C1159" s="1"/>
-      <c r="D1159" s="1"/>
-      <c r="E1159" s="1"/>
-      <c r="F1159" s="1"/>
-      <c r="G1159" s="1"/>
-      <c r="H1159" s="1"/>
+      <c r="A1159" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1159" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1159" s="2">
+        <v>9903217</v>
+      </c>
+      <c r="D1159" s="2">
+        <v>7061087</v>
+      </c>
+      <c r="E1159" s="5">
+        <v>46052.958333333336</v>
+      </c>
+      <c r="F1159" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1159" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1159" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1160" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1160" s="1"/>
-      <c r="C1160" s="1"/>
-      <c r="D1160" s="1"/>
-      <c r="E1160" s="1"/>
-      <c r="F1160" s="1"/>
-      <c r="G1160" s="1"/>
-      <c r="H1160" s="1"/>
+      <c r="A1160" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1160" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1160" s="2">
+        <v>9909696</v>
+      </c>
+      <c r="D1160" s="2">
+        <v>7681468</v>
+      </c>
+      <c r="E1160" s="5">
+        <v>46054.458333333336</v>
+      </c>
+      <c r="F1160" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1160" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1160" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="1161" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1161" s="1"/>
-      <c r="C1161" s="1"/>
-      <c r="D1161" s="1"/>
-      <c r="E1161" s="1"/>
-      <c r="F1161" s="1"/>
-      <c r="G1161" s="1"/>
-      <c r="H1161" s="1"/>
+      <c r="A1161" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1161" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1161" s="2">
+        <v>9907721</v>
+      </c>
+      <c r="D1161" s="2">
+        <v>7749008</v>
+      </c>
+      <c r="E1161" s="5">
+        <v>46054.458333333336</v>
+      </c>
+      <c r="F1161" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1161" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1161" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="1162" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1162" s="1"/>
-      <c r="C1162" s="1"/>
-      <c r="D1162" s="1"/>
-      <c r="E1162" s="1"/>
-      <c r="F1162" s="1"/>
-      <c r="G1162" s="1"/>
-      <c r="H1162" s="1"/>
+      <c r="A1162" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1162" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1162" s="2">
+        <v>9899420</v>
+      </c>
+      <c r="D1162" s="2">
+        <v>7733803</v>
+      </c>
+      <c r="E1162" s="5">
+        <v>46054.958333333336</v>
+      </c>
+      <c r="F1162" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1162" s="2">
+        <v>59</v>
+      </c>
+      <c r="H1162" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="1163" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1163" s="1"/>
-      <c r="C1163" s="1"/>
-      <c r="D1163" s="1"/>
-      <c r="E1163" s="1"/>
-      <c r="F1163" s="1"/>
-      <c r="G1163" s="1"/>
-      <c r="H1163" s="1"/>
+      <c r="A1163" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1163" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1163" s="2">
+        <v>9903746</v>
+      </c>
+      <c r="D1163" s="2">
+        <v>7736106</v>
+      </c>
+      <c r="E1163" s="5">
+        <v>46055.958333333336</v>
+      </c>
+      <c r="F1163" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1163" s="2">
+        <v>22</v>
+      </c>
+      <c r="H1163" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1164" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1164" s="1"/>
-      <c r="C1164" s="1"/>
-      <c r="D1164" s="1"/>
-      <c r="E1164" s="1"/>
-      <c r="F1164" s="1"/>
-      <c r="G1164" s="1"/>
-      <c r="H1164" s="1"/>
+      <c r="A1164" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1164" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1164" s="2">
+        <v>9901495</v>
+      </c>
+      <c r="D1164" s="2">
+        <v>7744027</v>
+      </c>
+      <c r="E1164" s="5">
+        <v>46056.958333333336</v>
+      </c>
+      <c r="F1164" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1164" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1164" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="1165" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1165" s="1"/>
-      <c r="C1165" s="1"/>
-      <c r="D1165" s="1"/>
-      <c r="E1165" s="1"/>
-      <c r="F1165" s="1"/>
-      <c r="G1165" s="1"/>
-      <c r="H1165" s="1"/>
+      <c r="A1165" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1165" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1165" s="2">
+        <v>9890777</v>
+      </c>
+      <c r="D1165" s="2">
+        <v>4740911</v>
+      </c>
+      <c r="E1165" s="5">
+        <v>46058.458333333336</v>
+      </c>
+      <c r="F1165" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1165" s="2">
+        <v>72</v>
+      </c>
+      <c r="H1165" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1166" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1166" s="1"/>
-      <c r="C1166" s="1"/>
-      <c r="D1166" s="1"/>
-      <c r="E1166" s="1"/>
-      <c r="F1166" s="1"/>
-      <c r="G1166" s="1"/>
-      <c r="H1166" s="1"/>
+      <c r="A1166" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1166" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1166" s="2">
+        <v>9917217</v>
+      </c>
+      <c r="D1166" s="2">
+        <v>7757100</v>
+      </c>
+      <c r="E1166" s="5">
+        <v>46058.458333333336</v>
+      </c>
+      <c r="F1166" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1166" s="2">
+        <v>25</v>
+      </c>
+      <c r="H1166" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="1167" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1167" s="1"/>
-      <c r="C1167" s="1"/>
-      <c r="D1167" s="1"/>
-      <c r="E1167" s="1"/>
-      <c r="F1167" s="1"/>
-      <c r="G1167" s="1"/>
-      <c r="H1167" s="1"/>
+      <c r="A1167" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1167" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1167" s="2">
+        <v>9863021</v>
+      </c>
+      <c r="D1167" s="2">
+        <v>4024230</v>
+      </c>
+      <c r="E1167" s="5">
+        <v>46058.458333333336</v>
+      </c>
+      <c r="F1167" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1167" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1167" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1168" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1168" s="1"/>
-      <c r="C1168" s="1"/>
-      <c r="D1168" s="1"/>
-      <c r="E1168" s="1"/>
-      <c r="F1168" s="1"/>
-      <c r="G1168" s="1"/>
-      <c r="H1168" s="1"/>
+      <c r="A1168" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1168" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1168" s="2">
+        <v>9891091</v>
+      </c>
+      <c r="D1168" s="2">
+        <v>7734734</v>
+      </c>
+      <c r="E1168" s="5">
+        <v>46059.958333333336</v>
+      </c>
+      <c r="F1168" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1168" s="2">
+        <v>64</v>
+      </c>
+      <c r="H1168" s="1" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="1169" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1169" s="1"/>
-      <c r="C1169" s="1"/>
-      <c r="D1169" s="1"/>
-      <c r="E1169" s="1"/>
-      <c r="F1169" s="1"/>
-      <c r="G1169" s="1"/>
-      <c r="H1169" s="1"/>
+      <c r="A1169" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1169" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1169" s="2">
+        <v>9922580</v>
+      </c>
+      <c r="D1169" s="2">
+        <v>7751447</v>
+      </c>
+      <c r="E1169" s="5">
+        <v>46060.458333333336</v>
+      </c>
+      <c r="F1169" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1169" s="2">
+        <v>48</v>
+      </c>
+      <c r="H1169" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1170" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1170" s="1"/>
-      <c r="C1170" s="1"/>
-      <c r="D1170" s="1"/>
-      <c r="E1170" s="1"/>
-      <c r="F1170" s="1"/>
-      <c r="G1170" s="1"/>
-      <c r="H1170" s="1"/>
+      <c r="A1170" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1170" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1170" s="2">
+        <v>9927508</v>
+      </c>
+      <c r="D1170" s="2">
+        <v>4011817</v>
+      </c>
+      <c r="E1170" s="5">
+        <v>46062.458333333336</v>
+      </c>
+      <c r="F1170" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1170" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1170" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1171" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1171" s="1"/>
-      <c r="C1171" s="1"/>
-      <c r="D1171" s="1"/>
-      <c r="E1171" s="1"/>
-      <c r="F1171" s="1"/>
-      <c r="G1171" s="1"/>
-      <c r="H1171" s="1"/>
+      <c r="A1171" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1171" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1171" s="2">
+        <v>9932547</v>
+      </c>
+      <c r="D1171" s="2">
+        <v>4238732</v>
+      </c>
+      <c r="E1171" s="5">
+        <v>46064.458333333336</v>
+      </c>
+      <c r="F1171" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1171" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1171" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="1172" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1172" s="1"/>
-      <c r="C1172" s="1"/>
-      <c r="D1172" s="1"/>
-      <c r="E1172" s="1"/>
-      <c r="F1172" s="1"/>
-      <c r="G1172" s="1"/>
-      <c r="H1172" s="1"/>
+      <c r="A1172" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1172" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1172" s="2">
+        <v>9932866</v>
+      </c>
+      <c r="D1172" s="2">
+        <v>6226231</v>
+      </c>
+      <c r="E1172" s="5">
+        <v>46064.458333333336</v>
+      </c>
+      <c r="F1172" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1172" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1172" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="1173" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1173" s="1"/>
-      <c r="C1173" s="1"/>
-      <c r="D1173" s="1"/>
-      <c r="E1173" s="1"/>
-      <c r="F1173" s="1"/>
-      <c r="G1173" s="1"/>
-      <c r="H1173" s="1"/>
+      <c r="A1173" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1173" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1173" s="2">
+        <v>9929653</v>
+      </c>
+      <c r="D1173" s="2">
+        <v>4186328</v>
+      </c>
+      <c r="E1173" s="5">
+        <v>46064.958333333336</v>
+      </c>
+      <c r="F1173" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1173" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1173" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1174" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1174" s="1"/>
-      <c r="C1174" s="1"/>
-      <c r="D1174" s="1"/>
-      <c r="E1174" s="1"/>
-      <c r="F1174" s="1"/>
-      <c r="G1174" s="1"/>
-      <c r="H1174" s="1"/>
+      <c r="A1174" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1174" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1174" s="2">
+        <v>9776283</v>
+      </c>
+      <c r="D1174" s="2">
+        <v>7235999</v>
+      </c>
+      <c r="E1174" s="5">
+        <v>46066.458333333336</v>
+      </c>
+      <c r="F1174" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1174" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1174" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1175" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1175" s="1"/>
-      <c r="C1175" s="1"/>
-      <c r="D1175" s="1"/>
-      <c r="E1175" s="1"/>
-      <c r="F1175" s="1"/>
-      <c r="G1175" s="1"/>
-      <c r="H1175" s="1"/>
+      <c r="A1175" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1175" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1175" s="2">
+        <v>9935975</v>
+      </c>
+      <c r="D1175" s="2">
+        <v>4049812</v>
+      </c>
+      <c r="E1175" s="5">
+        <v>46066.458333333336</v>
+      </c>
+      <c r="F1175" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1175" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1175" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="1176" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1176" s="1"/>
-      <c r="C1176" s="1"/>
-      <c r="D1176" s="1"/>
-      <c r="E1176" s="1"/>
-      <c r="F1176" s="1"/>
-      <c r="G1176" s="1"/>
-      <c r="H1176" s="1"/>
+      <c r="A1176" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1176" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1176" s="2">
+        <v>9940185</v>
+      </c>
+      <c r="D1176" s="2">
+        <v>7044033</v>
+      </c>
+      <c r="E1176" s="5">
+        <v>46067.958333333336</v>
+      </c>
+      <c r="F1176" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1176" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1176" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1177" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1177" s="1"/>
-      <c r="C1177" s="1"/>
-      <c r="D1177" s="1"/>
-      <c r="E1177" s="1"/>
-      <c r="F1177" s="1"/>
-      <c r="G1177" s="1"/>
-      <c r="H1177" s="1"/>
+      <c r="A1177" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1177" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1177" s="2">
+        <v>9944270</v>
+      </c>
+      <c r="D1177" s="2">
+        <v>4281763</v>
+      </c>
+      <c r="E1177" s="5">
+        <v>46069.958333333336</v>
+      </c>
+      <c r="F1177" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1177" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1177" s="1" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="1178" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1178" s="1"/>
-      <c r="C1178" s="1"/>
-      <c r="D1178" s="1"/>
-      <c r="E1178" s="1"/>
-      <c r="F1178" s="1"/>
-      <c r="G1178" s="1"/>
-      <c r="H1178" s="1"/>
+      <c r="A1178" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1178" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1178" s="2">
+        <v>9945821</v>
+      </c>
+      <c r="D1178" s="2">
+        <v>5254415</v>
+      </c>
+      <c r="E1178" s="5">
+        <v>46071.958333333336</v>
+      </c>
+      <c r="F1178" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1178" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1178" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="1179" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1179" s="1"/>
-      <c r="C1179" s="1"/>
-      <c r="D1179" s="1"/>
-      <c r="E1179" s="1"/>
-      <c r="F1179" s="1"/>
-      <c r="G1179" s="1"/>
-      <c r="H1179" s="1"/>
+      <c r="A1179" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1179" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1179" s="2">
+        <v>9955513</v>
+      </c>
+      <c r="D1179" s="2">
+        <v>7066929</v>
+      </c>
+      <c r="E1179" s="5">
+        <v>46075.458333333336</v>
+      </c>
+      <c r="F1179" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1179" s="2">
+        <v>21</v>
+      </c>
+      <c r="H1179" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1180" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1180" s="1"/>
-      <c r="C1180" s="1"/>
-      <c r="D1180" s="1"/>
-      <c r="E1180" s="1"/>
-      <c r="F1180" s="1"/>
-      <c r="G1180" s="1"/>
-      <c r="H1180" s="1"/>
+      <c r="A1180" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1180" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1180" s="2">
+        <v>9958131</v>
+      </c>
+      <c r="D1180" s="2">
+        <v>5335119</v>
+      </c>
+      <c r="E1180" s="5">
+        <v>46076.958333333336</v>
+      </c>
+      <c r="F1180" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1180" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1180" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="1181" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1181" s="1"/>
-      <c r="C1181" s="1"/>
-      <c r="D1181" s="1"/>
-      <c r="E1181" s="1"/>
-      <c r="F1181" s="1"/>
-      <c r="G1181" s="1"/>
-      <c r="H1181" s="1"/>
+      <c r="A1181" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1181" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1181" s="2">
+        <v>9961729</v>
+      </c>
+      <c r="D1181" s="2">
+        <v>4814884</v>
+      </c>
+      <c r="E1181" s="5">
+        <v>46078.458333333336</v>
+      </c>
+      <c r="F1181" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1181" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1181" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1182" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1182" s="1"/>
-      <c r="C1182" s="1"/>
-      <c r="D1182" s="1"/>
-      <c r="E1182" s="1"/>
-      <c r="F1182" s="1"/>
-      <c r="G1182" s="1"/>
-      <c r="H1182" s="1"/>
+      <c r="A1182" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1182" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1182" s="2">
+        <v>9963559</v>
+      </c>
+      <c r="D1182" s="2">
+        <v>7759958</v>
+      </c>
+      <c r="E1182" s="5">
+        <v>46079.958333333336</v>
+      </c>
+      <c r="F1182" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1182" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1182" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1183" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1183" s="1"/>
-      <c r="C1183" s="1"/>
-      <c r="D1183" s="1"/>
-      <c r="E1183" s="1"/>
-      <c r="F1183" s="1"/>
-      <c r="G1183" s="1"/>
-      <c r="H1183" s="1"/>
+      <c r="A1183" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1183" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1183" s="2">
+        <v>9965063</v>
+      </c>
+      <c r="D1183" s="2">
+        <v>5412544</v>
+      </c>
+      <c r="E1183" s="5">
+        <v>46079.958333333336</v>
+      </c>
+      <c r="F1183" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1183" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1183" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="1184" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1184" s="1"/>
-      <c r="C1184" s="1"/>
-      <c r="D1184" s="1"/>
-      <c r="E1184" s="1"/>
-      <c r="F1184" s="1"/>
-      <c r="G1184" s="1"/>
-      <c r="H1184" s="1"/>
+      <c r="A1184" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1184" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1184" s="2">
+        <v>9965895</v>
+      </c>
+      <c r="D1184" s="2">
+        <v>6306745</v>
+      </c>
+      <c r="E1184" s="5">
+        <v>46080.458333333336</v>
+      </c>
+      <c r="F1184" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1184" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1184" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1185" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1185" s="1"/>
-      <c r="C1185" s="1"/>
-      <c r="D1185" s="1"/>
-      <c r="E1185" s="1"/>
-      <c r="F1185" s="1"/>
-      <c r="G1185" s="1"/>
-      <c r="H1185" s="1"/>
+      <c r="A1185" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1185" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1185" s="2">
+        <v>9969315</v>
+      </c>
+      <c r="D1185" s="2">
+        <v>6715862</v>
+      </c>
+      <c r="E1185" s="5">
+        <v>46082.458333333336</v>
+      </c>
+      <c r="F1185" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1185" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1185" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="1186" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1186" s="1"/>
-      <c r="C1186" s="1"/>
-      <c r="D1186" s="1"/>
-      <c r="E1186" s="1"/>
-      <c r="F1186" s="1"/>
-      <c r="G1186" s="1"/>
-      <c r="H1186" s="1"/>
+      <c r="A1186" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1186" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1186" s="2">
+        <v>9972091</v>
+      </c>
+      <c r="D1186" s="2">
+        <v>7807550</v>
+      </c>
+      <c r="E1186" s="5">
+        <v>46082.958333333336</v>
+      </c>
+      <c r="F1186" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1186" s="2">
+        <v>22</v>
+      </c>
+      <c r="H1186" s="1" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="1187" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1187" s="1"/>
-      <c r="C1187" s="1"/>
-      <c r="D1187" s="1"/>
-      <c r="E1187" s="1"/>
-      <c r="F1187" s="1"/>
-      <c r="G1187" s="1"/>
-      <c r="H1187" s="1"/>
+      <c r="A1187" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1187" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1187" s="2">
+        <v>9966424</v>
+      </c>
+      <c r="D1187" s="2">
+        <v>4740911</v>
+      </c>
+      <c r="E1187" s="5">
+        <v>46083.958333333336</v>
+      </c>
+      <c r="F1187" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1187" s="2">
+        <v>72</v>
+      </c>
+      <c r="H1187" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1188" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1188" s="1"/>
-      <c r="C1188" s="1"/>
-      <c r="D1188" s="1"/>
-      <c r="E1188" s="1"/>
-      <c r="F1188" s="1"/>
-      <c r="G1188" s="1"/>
-      <c r="H1188" s="1"/>
+      <c r="A1188" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1188" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1188" s="2">
+        <v>9974609</v>
+      </c>
+      <c r="D1188" s="2">
+        <v>6110990</v>
+      </c>
+      <c r="E1188" s="5">
+        <v>46084.458333333336</v>
+      </c>
+      <c r="F1188" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1188" s="2">
+        <v>43</v>
+      </c>
+      <c r="H1188" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="1189" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1189" s="1"/>
-      <c r="C1189" s="1"/>
-      <c r="D1189" s="1"/>
-      <c r="E1189" s="1"/>
-      <c r="F1189" s="1"/>
-      <c r="G1189" s="1"/>
-      <c r="H1189" s="1"/>
+      <c r="A1189" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1189" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1189" s="2">
+        <v>9985732</v>
+      </c>
+      <c r="D1189" s="2">
+        <v>7821165</v>
+      </c>
+      <c r="E1189" s="5">
+        <v>46088.958333333336</v>
+      </c>
+      <c r="F1189" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1189" s="2">
+        <v>43</v>
+      </c>
+      <c r="H1189" s="1" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="1190" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1190" s="1"/>
-      <c r="C1190" s="1"/>
-      <c r="D1190" s="1"/>
-      <c r="E1190" s="1"/>
-      <c r="F1190" s="1"/>
-      <c r="G1190" s="1"/>
-      <c r="H1190" s="1"/>
+      <c r="A1190" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1190" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1190" s="2">
+        <v>9948870</v>
+      </c>
+      <c r="D1190" s="2">
+        <v>7785882</v>
+      </c>
+      <c r="E1190" s="5">
+        <v>46088.958333333336</v>
+      </c>
+      <c r="F1190" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1190" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1190" s="1" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="1191" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1191" s="1"/>
-      <c r="C1191" s="1"/>
-      <c r="D1191" s="1"/>
-      <c r="E1191" s="1"/>
-      <c r="F1191" s="1"/>
-      <c r="G1191" s="1"/>
-      <c r="H1191" s="1"/>
+      <c r="A1191" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1191" s="2">
+        <v>9988824</v>
+      </c>
+      <c r="D1191" s="2">
+        <v>4268108</v>
+      </c>
+      <c r="E1191" s="5">
+        <v>46090.958333333336</v>
+      </c>
+      <c r="F1191" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1191" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1191" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1192" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1192" s="1"/>
-      <c r="C1192" s="1"/>
-      <c r="D1192" s="1"/>
-      <c r="E1192" s="1"/>
-      <c r="F1192" s="1"/>
-      <c r="G1192" s="1"/>
-      <c r="H1192" s="1"/>
+      <c r="A1192" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1192" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1192" s="2">
+        <v>9997046</v>
+      </c>
+      <c r="D1192" s="2">
+        <v>7832254</v>
+      </c>
+      <c r="E1192" s="5">
+        <v>46094.458333333336</v>
+      </c>
+      <c r="F1192" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1192" s="2">
+        <v>42</v>
+      </c>
+      <c r="H1192" s="2">
+        <v>3117</v>
+      </c>
     </row>
     <row r="1193" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1193" s="1"/>
-      <c r="C1193" s="1"/>
-      <c r="D1193" s="1"/>
-      <c r="E1193" s="1"/>
-      <c r="F1193" s="1"/>
-      <c r="G1193" s="1"/>
-      <c r="H1193" s="1"/>
+      <c r="A1193" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1193" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1193" s="2">
+        <v>9996278</v>
+      </c>
+      <c r="D1193" s="2">
+        <v>4581376</v>
+      </c>
+      <c r="E1193" s="5">
+        <v>46094.958333333336</v>
+      </c>
+      <c r="F1193" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1193" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1193" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="1194" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1194" s="1"/>
-      <c r="C1194" s="1"/>
-      <c r="D1194" s="1"/>
-      <c r="E1194" s="1"/>
-      <c r="F1194" s="1"/>
-      <c r="G1194" s="1"/>
-      <c r="H1194" s="1"/>
+      <c r="A1194" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1194" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1194" s="2">
+        <v>9962331</v>
+      </c>
+      <c r="D1194" s="2">
+        <v>3570964</v>
+      </c>
+      <c r="E1194" s="5">
+        <v>46094.958333333336</v>
+      </c>
+      <c r="F1194" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1194" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1194" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1195" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1195" s="1"/>
-      <c r="C1195" s="1"/>
-      <c r="D1195" s="1"/>
-      <c r="E1195" s="1"/>
-      <c r="F1195" s="1"/>
-      <c r="G1195" s="1"/>
-      <c r="H1195" s="1"/>
+      <c r="A1195" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1195" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1195" s="2">
+        <v>10001538</v>
+      </c>
+      <c r="D1195" s="2">
+        <v>4049812</v>
+      </c>
+      <c r="E1195" s="5">
+        <v>46096.958333333336</v>
+      </c>
+      <c r="F1195" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1195" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1195" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="1196" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1196" s="1"/>
-      <c r="C1196" s="1"/>
-      <c r="D1196" s="1"/>
-      <c r="E1196" s="1"/>
-      <c r="F1196" s="1"/>
-      <c r="G1196" s="1"/>
-      <c r="H1196" s="1"/>
+      <c r="A1196" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1196" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1196" s="2">
+        <v>9990319</v>
+      </c>
+      <c r="D1196" s="2">
+        <v>7825630</v>
+      </c>
+      <c r="E1196" s="5">
+        <v>46100.958333333336</v>
+      </c>
+      <c r="F1196" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1196" s="2">
+        <v>58</v>
+      </c>
+      <c r="H1196" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1197" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1197" s="1"/>
-      <c r="C1197" s="1"/>
-      <c r="D1197" s="1"/>
-      <c r="E1197" s="1"/>
-      <c r="F1197" s="1"/>
-      <c r="G1197" s="1"/>
-      <c r="H1197" s="1"/>
+      <c r="A1197" s="2">
+        <v>1346628</v>
+      </c>
+      <c r="B1197" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1197" s="2">
+        <v>10001558</v>
+      </c>
+      <c r="D1197" s="2">
+        <v>5913784</v>
+      </c>
+      <c r="E1197" s="5">
+        <v>46102.458333333336</v>
+      </c>
+      <c r="F1197" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1197" s="2">
+        <v>48</v>
+      </c>
+      <c r="H1197" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1198" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1198" s="1"/>
-      <c r="C1198" s="1"/>
-      <c r="D1198" s="1"/>
-      <c r="E1198" s="1"/>
-      <c r="F1198" s="1"/>
-      <c r="G1198" s="1"/>
-      <c r="H1198" s="1"/>
+      <c r="A1198" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1198" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1198" s="2">
+        <v>10017370</v>
+      </c>
+      <c r="D1198" s="2">
+        <v>5317029</v>
+      </c>
+      <c r="E1198" s="5">
+        <v>46102.958333333336</v>
+      </c>
+      <c r="F1198" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1198" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1198" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1199" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1199" s="1"/>
-      <c r="C1199" s="1"/>
-      <c r="D1199" s="1"/>
-      <c r="E1199" s="1"/>
-      <c r="F1199" s="1"/>
-      <c r="G1199" s="1"/>
-      <c r="H1199" s="1"/>
+      <c r="A1199" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1199" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1199" s="2">
+        <v>10018379</v>
+      </c>
+      <c r="D1199" s="2">
+        <v>7036013</v>
+      </c>
+      <c r="E1199" s="5">
+        <v>46103.458333333336</v>
+      </c>
+      <c r="F1199" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1199" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1199" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="1200" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1200" s="1"/>
-      <c r="C1200" s="1"/>
-      <c r="D1200" s="1"/>
-      <c r="E1200" s="1"/>
-      <c r="F1200" s="1"/>
-      <c r="G1200" s="1"/>
-      <c r="H1200" s="1"/>
+      <c r="A1200" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1200" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1200" s="2">
+        <v>10018433</v>
+      </c>
+      <c r="D1200" s="2">
+        <v>7036013</v>
+      </c>
+      <c r="E1200" s="5">
+        <v>46103.458333333336</v>
+      </c>
+      <c r="F1200" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1200" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1200" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="1201" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1201" s="1"/>
-      <c r="C1201" s="1"/>
-      <c r="D1201" s="1"/>
-      <c r="E1201" s="1"/>
-      <c r="F1201" s="1"/>
-      <c r="G1201" s="1"/>
-      <c r="H1201" s="1"/>
+      <c r="A1201" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1201" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1201" s="2">
+        <v>10018934</v>
+      </c>
+      <c r="D1201" s="2">
+        <v>5913784</v>
+      </c>
+      <c r="E1201" s="5">
+        <v>46103.958333333336</v>
+      </c>
+      <c r="F1201" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1201" s="2">
+        <v>48</v>
+      </c>
+      <c r="H1201" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1202" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1202" s="1"/>
-      <c r="C1202" s="1"/>
-      <c r="D1202" s="1"/>
-      <c r="E1202" s="1"/>
-      <c r="F1202" s="1"/>
-      <c r="G1202" s="1"/>
-      <c r="H1202" s="1"/>
+      <c r="A1202" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1202" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1202" s="2">
+        <v>10028798</v>
+      </c>
+      <c r="D1202" s="2">
+        <v>6981590</v>
+      </c>
+      <c r="E1202" s="5">
+        <v>46107.958333333336</v>
+      </c>
+      <c r="F1202" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1202" s="2">
+        <v>49</v>
+      </c>
+      <c r="H1202" s="1" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="1203" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1203" s="1"/>
-      <c r="C1203" s="1"/>
-      <c r="D1203" s="1"/>
-      <c r="E1203" s="1"/>
-      <c r="F1203" s="1"/>
-      <c r="G1203" s="1"/>
-      <c r="H1203" s="1"/>
+      <c r="A1203" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1203" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1203" s="2">
+        <v>9963666</v>
+      </c>
+      <c r="D1203" s="2">
+        <v>3570964</v>
+      </c>
+      <c r="E1203" s="5">
+        <v>46108.958333333336</v>
+      </c>
+      <c r="F1203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1203" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1203" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1204" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1204" s="1"/>
-      <c r="C1204" s="1"/>
-      <c r="D1204" s="1"/>
-      <c r="E1204" s="1"/>
-      <c r="F1204" s="1"/>
-      <c r="G1204" s="1"/>
-      <c r="H1204" s="1"/>
+      <c r="A1204" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1204" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1204" s="2">
+        <v>10037878</v>
+      </c>
+      <c r="D1204" s="2">
+        <v>7329929</v>
+      </c>
+      <c r="E1204" s="5">
+        <v>46111.416666666664</v>
+      </c>
+      <c r="F1204" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1204" s="2">
+        <v>20</v>
+      </c>
+      <c r="H1204" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1205" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1205" s="1"/>
-      <c r="C1205" s="1"/>
-      <c r="D1205" s="1"/>
-      <c r="E1205" s="1"/>
-      <c r="F1205" s="1"/>
-      <c r="G1205" s="1"/>
-      <c r="H1205" s="1"/>
+      <c r="A1205" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1205" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1205" s="2">
+        <v>9937112</v>
+      </c>
+      <c r="D1205" s="2">
+        <v>4024230</v>
+      </c>
+      <c r="E1205" s="5">
+        <v>46112.916666666664</v>
+      </c>
+      <c r="F1205" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1205" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1205" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1206" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1206" s="1"/>
-      <c r="C1206" s="1"/>
-      <c r="D1206" s="1"/>
-      <c r="E1206" s="1"/>
-      <c r="F1206" s="1"/>
-      <c r="G1206" s="1"/>
-      <c r="H1206" s="1"/>
+      <c r="A1206" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1206" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1206" s="2">
+        <v>9954776</v>
+      </c>
+      <c r="D1206" s="2">
+        <v>4740911</v>
+      </c>
+      <c r="E1206" s="5">
+        <v>46112.916666666664</v>
+      </c>
+      <c r="F1206" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1206" s="2">
+        <v>72</v>
+      </c>
+      <c r="H1206" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1207" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1207" s="1"/>
-      <c r="C1207" s="1"/>
-      <c r="D1207" s="1"/>
-      <c r="E1207" s="1"/>
-      <c r="F1207" s="1"/>
-      <c r="G1207" s="1"/>
-      <c r="H1207" s="1"/>
+      <c r="A1207" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1207" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1207" s="2">
+        <v>10022379</v>
+      </c>
+      <c r="D1207" s="2">
+        <v>7806921</v>
+      </c>
+      <c r="E1207" s="5">
+        <v>46113.416666666664</v>
+      </c>
+      <c r="F1207" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1207" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1207" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1208" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1208" s="1"/>
-      <c r="C1208" s="1"/>
-      <c r="D1208" s="1"/>
-      <c r="E1208" s="1"/>
-      <c r="F1208" s="1"/>
-      <c r="G1208" s="1"/>
-      <c r="H1208" s="1"/>
+      <c r="A1208" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1208" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1208" s="2">
+        <v>10045419</v>
+      </c>
+      <c r="D1208" s="2">
+        <v>7855347</v>
+      </c>
+      <c r="E1208" s="5">
+        <v>46114.416666666664</v>
+      </c>
+      <c r="F1208" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1208" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1208" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="1209" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1209" s="1"/>
-      <c r="C1209" s="1"/>
-      <c r="D1209" s="1"/>
-      <c r="E1209" s="1"/>
-      <c r="F1209" s="1"/>
-      <c r="G1209" s="1"/>
-      <c r="H1209" s="1"/>
+      <c r="A1209" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1209" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1209" s="2">
+        <v>10044607</v>
+      </c>
+      <c r="D1209" s="2">
+        <v>6504924</v>
+      </c>
+      <c r="E1209" s="5">
+        <v>46114.416666666664</v>
+      </c>
+      <c r="F1209" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1209" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1209" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="1210" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1210" s="1"/>
-      <c r="C1210" s="1"/>
-      <c r="D1210" s="1"/>
-      <c r="E1210" s="1"/>
-      <c r="F1210" s="1"/>
-      <c r="G1210" s="1"/>
-      <c r="H1210" s="1"/>
+      <c r="A1210" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1210" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1210" s="2">
+        <v>10040901</v>
+      </c>
+      <c r="D1210" s="2">
+        <v>7514006</v>
+      </c>
+      <c r="E1210" s="5">
+        <v>46115.416666666664</v>
+      </c>
+      <c r="F1210" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1210" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1210" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1211" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1211" s="1"/>
-      <c r="C1211" s="1"/>
-      <c r="D1211" s="1"/>
-      <c r="E1211" s="1"/>
-      <c r="F1211" s="1"/>
-      <c r="G1211" s="1"/>
-      <c r="H1211" s="1"/>
+      <c r="A1211" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1211" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1211" s="2">
+        <v>10052529</v>
+      </c>
+      <c r="D1211" s="2">
+        <v>6504924</v>
+      </c>
+      <c r="E1211" s="5">
+        <v>46117.416666666664</v>
+      </c>
+      <c r="F1211" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1211" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1211" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="1212" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1212" s="1"/>
-      <c r="C1212" s="1"/>
-      <c r="D1212" s="1"/>
-      <c r="E1212" s="1"/>
-      <c r="F1212" s="1"/>
-      <c r="G1212" s="1"/>
-      <c r="H1212" s="1"/>
+      <c r="A1212" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1212" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1212" s="2">
+        <v>10054329</v>
+      </c>
+      <c r="D1212" s="2">
+        <v>7855347</v>
+      </c>
+      <c r="E1212" s="5">
+        <v>46117.916666666664</v>
+      </c>
+      <c r="F1212" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1212" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1212" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="1213" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1213" s="1"/>
-      <c r="C1213" s="1"/>
-      <c r="D1213" s="1"/>
-      <c r="E1213" s="1"/>
-      <c r="F1213" s="1"/>
-      <c r="G1213" s="1"/>
-      <c r="H1213" s="1"/>
+      <c r="A1213" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1213" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1213" s="2">
+        <v>10060019</v>
+      </c>
+      <c r="D1213" s="2">
+        <v>7893984</v>
+      </c>
+      <c r="E1213" s="5">
+        <v>46120.416666666664</v>
+      </c>
+      <c r="F1213" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1213" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1213" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="1214" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1214" s="1"/>
-      <c r="C1214" s="1"/>
-      <c r="D1214" s="1"/>
-      <c r="E1214" s="1"/>
-      <c r="F1214" s="1"/>
-      <c r="G1214" s="1"/>
-      <c r="H1214" s="1"/>
+      <c r="A1214" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1214" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1214" s="2">
+        <v>10061811</v>
+      </c>
+      <c r="D1214" s="2">
+        <v>7292190</v>
+      </c>
+      <c r="E1214" s="5">
+        <v>46121.416666666664</v>
+      </c>
+      <c r="F1214" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1214" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1214" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1215" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1215" s="1"/>
-      <c r="C1215" s="1"/>
-      <c r="D1215" s="1"/>
-      <c r="E1215" s="1"/>
-      <c r="F1215" s="1"/>
-      <c r="G1215" s="1"/>
-      <c r="H1215" s="1"/>
+      <c r="A1215" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1215" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1215" s="2">
+        <v>10075543</v>
+      </c>
+      <c r="D1215" s="2">
+        <v>7292190</v>
+      </c>
+      <c r="E1215" s="5">
+        <v>46126.916666666664</v>
+      </c>
+      <c r="F1215" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1215" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1215" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1216" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1216" s="1"/>
-      <c r="C1216" s="1"/>
-      <c r="D1216" s="1"/>
-      <c r="E1216" s="1"/>
-      <c r="F1216" s="1"/>
-      <c r="G1216" s="1"/>
-      <c r="H1216" s="1"/>
+      <c r="A1216" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1216" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1216" s="2">
+        <v>10077045</v>
+      </c>
+      <c r="D1216" s="2">
+        <v>6973319</v>
+      </c>
+      <c r="E1216" s="5">
+        <v>46128.416666666664</v>
+      </c>
+      <c r="F1216" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1216" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1216" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1217" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1217" s="1"/>
-      <c r="C1217" s="1"/>
-      <c r="D1217" s="1"/>
-      <c r="E1217" s="1"/>
-      <c r="F1217" s="1"/>
-      <c r="G1217" s="1"/>
-      <c r="H1217" s="1"/>
+      <c r="A1217" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1217" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1217" s="2">
+        <v>10080443</v>
+      </c>
+      <c r="D1217" s="2">
+        <v>7751319</v>
+      </c>
+      <c r="E1217" s="5">
+        <v>46129.416666666664</v>
+      </c>
+      <c r="F1217" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1217" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1217" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="1218" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1218" s="1"/>
-      <c r="C1218" s="1"/>
-      <c r="D1218" s="1"/>
-      <c r="E1218" s="1"/>
-      <c r="F1218" s="1"/>
-      <c r="G1218" s="1"/>
-      <c r="H1218" s="1"/>
+      <c r="A1218" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1218" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1218" s="2">
+        <v>10069599</v>
+      </c>
+      <c r="D1218" s="2">
+        <v>4740911</v>
+      </c>
+      <c r="E1218" s="5">
+        <v>46129.416666666664</v>
+      </c>
+      <c r="F1218" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1218" s="2">
+        <v>72</v>
+      </c>
+      <c r="H1218" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1219" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1219" s="1"/>
-      <c r="C1219" s="1"/>
-      <c r="D1219" s="1"/>
-      <c r="E1219" s="1"/>
-      <c r="F1219" s="1"/>
-      <c r="G1219" s="1"/>
-      <c r="H1219" s="1"/>
+      <c r="A1219" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1219" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1219" s="2">
+        <v>10084966</v>
+      </c>
+      <c r="D1219" s="2">
+        <v>7916202</v>
+      </c>
+      <c r="E1219" s="5">
+        <v>46130.916666666664</v>
+      </c>
+      <c r="F1219" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1219" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1219" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="1220" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1220" s="1"/>
-      <c r="C1220" s="1"/>
-      <c r="D1220" s="1"/>
-      <c r="E1220" s="1"/>
-      <c r="F1220" s="1"/>
-      <c r="G1220" s="1"/>
-      <c r="H1220" s="1"/>
+      <c r="A1220" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1220" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1220" s="2">
+        <v>10085611</v>
+      </c>
+      <c r="D1220" s="2">
+        <v>4245545</v>
+      </c>
+      <c r="E1220" s="5">
+        <v>46131.916666666664</v>
+      </c>
+      <c r="F1220" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1220" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1220" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1221" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1221" s="1"/>
-      <c r="C1221" s="1"/>
-      <c r="D1221" s="1"/>
-      <c r="E1221" s="1"/>
-      <c r="F1221" s="1"/>
-      <c r="G1221" s="1"/>
-      <c r="H1221" s="1"/>
+      <c r="A1221" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1221" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1221" s="2">
+        <v>10090033</v>
+      </c>
+      <c r="D1221" s="2">
+        <v>7292190</v>
+      </c>
+      <c r="E1221" s="5">
+        <v>46133.416666666664</v>
+      </c>
+      <c r="F1221" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1221" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1221" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1222" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1222" s="1"/>
-      <c r="C1222" s="1"/>
-      <c r="D1222" s="1"/>
-      <c r="E1222" s="1"/>
-      <c r="F1222" s="1"/>
-      <c r="G1222" s="1"/>
-      <c r="H1222" s="1"/>
+      <c r="A1222" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1222" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1222" s="2">
+        <v>10092343</v>
+      </c>
+      <c r="D1222" s="2">
+        <v>7283957</v>
+      </c>
+      <c r="E1222" s="5">
+        <v>46134.416666666664</v>
+      </c>
+      <c r="F1222" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1222" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1222" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1223" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1223" s="1"/>
-      <c r="C1223" s="1"/>
-      <c r="D1223" s="1"/>
-      <c r="E1223" s="1"/>
-      <c r="F1223" s="1"/>
-      <c r="G1223" s="1"/>
-      <c r="H1223" s="1"/>
+      <c r="A1223" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1223" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1223" s="2">
+        <v>10082565</v>
+      </c>
+      <c r="D1223" s="2">
+        <v>4102383</v>
+      </c>
+      <c r="E1223" s="5">
+        <v>46135.916666666664</v>
+      </c>
+      <c r="F1223" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1223" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1223" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1224" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1224" s="1"/>
-      <c r="C1224" s="1"/>
-      <c r="D1224" s="1"/>
-      <c r="E1224" s="1"/>
-      <c r="F1224" s="1"/>
-      <c r="G1224" s="1"/>
-      <c r="H1224" s="1"/>
+      <c r="A1224" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1224" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1224" s="2">
+        <v>10096836</v>
+      </c>
+      <c r="D1224" s="2">
+        <v>6067855</v>
+      </c>
+      <c r="E1224" s="5">
+        <v>46135.916666666664</v>
+      </c>
+      <c r="F1224" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1224" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1224" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1225" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1225" s="1"/>
-      <c r="C1225" s="1"/>
-      <c r="D1225" s="1"/>
-      <c r="E1225" s="1"/>
-      <c r="F1225" s="1"/>
-      <c r="G1225" s="1"/>
-      <c r="H1225" s="1"/>
+      <c r="A1225" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1225" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1225" s="2">
+        <v>10096651</v>
+      </c>
+      <c r="D1225" s="2">
+        <v>7086066</v>
+      </c>
+      <c r="E1225" s="5">
+        <v>46136.916666666664</v>
+      </c>
+      <c r="F1225" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1225" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1225" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1226" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1226" s="1"/>
-      <c r="C1226" s="1"/>
-      <c r="D1226" s="1"/>
-      <c r="E1226" s="1"/>
-      <c r="F1226" s="1"/>
-      <c r="G1226" s="1"/>
-      <c r="H1226" s="1"/>
+      <c r="A1226" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1226" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1226" s="2">
+        <v>10099872</v>
+      </c>
+      <c r="D1226" s="2">
+        <v>6227119</v>
+      </c>
+      <c r="E1226" s="5">
+        <v>46137.416666666664</v>
+      </c>
+      <c r="F1226" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1226" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1226" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1227" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1227" s="1"/>
-      <c r="C1227" s="1"/>
-      <c r="D1227" s="1"/>
-      <c r="E1227" s="1"/>
-      <c r="F1227" s="1"/>
-      <c r="G1227" s="1"/>
-      <c r="H1227" s="1"/>
+      <c r="A1227" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1227" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1227" s="2">
+        <v>10103942</v>
+      </c>
+      <c r="D1227" s="2">
+        <v>5317029</v>
+      </c>
+      <c r="E1227" s="5">
+        <v>46139.416666666664</v>
+      </c>
+      <c r="F1227" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1227" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1227" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1228" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1228" s="1"/>
-      <c r="C1228" s="1"/>
-      <c r="D1228" s="1"/>
-      <c r="E1228" s="1"/>
-      <c r="F1228" s="1"/>
-      <c r="G1228" s="1"/>
-      <c r="H1228" s="1"/>
+      <c r="A1228" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1228" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1228" s="2">
+        <v>10105106</v>
+      </c>
+      <c r="D1228" s="2">
+        <v>4296074</v>
+      </c>
+      <c r="E1228" s="5">
+        <v>46139.416666666664</v>
+      </c>
+      <c r="F1228" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1228" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1228" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="1229" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1229" s="1"/>
-      <c r="C1229" s="1"/>
-      <c r="D1229" s="1"/>
-      <c r="E1229" s="1"/>
-      <c r="F1229" s="1"/>
-      <c r="G1229" s="1"/>
-      <c r="H1229" s="1"/>
+      <c r="A1229" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1229" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1229" s="2">
+        <v>10087790</v>
+      </c>
+      <c r="D1229" s="2">
+        <v>7235999</v>
+      </c>
+      <c r="E1229" s="5">
+        <v>46139.416666666664</v>
+      </c>
+      <c r="F1229" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1229" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1229" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1230" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1230" s="1"/>
-      <c r="C1230" s="1"/>
-      <c r="D1230" s="1"/>
-      <c r="E1230" s="1"/>
-      <c r="F1230" s="1"/>
-      <c r="G1230" s="1"/>
-      <c r="H1230" s="1"/>
+      <c r="A1230" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1230" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1230" s="2">
+        <v>10112221</v>
+      </c>
+      <c r="D1230" s="2">
+        <v>6201443</v>
+      </c>
+      <c r="E1230" s="5">
+        <v>46141.916666666664</v>
+      </c>
+      <c r="F1230" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1230" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1230" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1231" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1231" s="1"/>
-      <c r="C1231" s="1"/>
-      <c r="D1231" s="1"/>
-      <c r="E1231" s="1"/>
-      <c r="F1231" s="1"/>
-      <c r="G1231" s="1"/>
-      <c r="H1231" s="1"/>
+      <c r="A1231" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1231" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1231" s="2">
+        <v>10002127</v>
+      </c>
+      <c r="D1231" s="2">
+        <v>4024230</v>
+      </c>
+      <c r="E1231" s="5">
+        <v>46142.416666666664</v>
+      </c>
+      <c r="F1231" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1231" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1231" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1232" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1232" s="1"/>
-      <c r="C1232" s="1"/>
-      <c r="D1232" s="1"/>
-      <c r="E1232" s="1"/>
-      <c r="F1232" s="1"/>
-      <c r="G1232" s="1"/>
-      <c r="H1232" s="1"/>
+      <c r="A1232" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1232" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1232" s="2">
+        <v>10053352</v>
+      </c>
+      <c r="D1232" s="2">
+        <v>4199493</v>
+      </c>
+      <c r="E1232" s="5">
+        <v>46142.416666666664</v>
+      </c>
+      <c r="F1232" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1232" s="2">
+        <v>38</v>
+      </c>
+      <c r="H1232" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="1233" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1233" s="1"/>
-      <c r="C1233" s="1"/>
-      <c r="D1233" s="1"/>
-      <c r="E1233" s="1"/>
-      <c r="F1233" s="1"/>
-      <c r="G1233" s="1"/>
-      <c r="H1233" s="1"/>
+      <c r="A1233" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1233" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1233" s="2">
+        <v>10113715</v>
+      </c>
+      <c r="D1233" s="2">
+        <v>7086066</v>
+      </c>
+      <c r="E1233" s="5">
+        <v>46142.916666666664</v>
+      </c>
+      <c r="F1233" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1233" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1233" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1234" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1234" s="1"/>
-      <c r="C1234" s="1"/>
-      <c r="D1234" s="1"/>
-      <c r="E1234" s="1"/>
-      <c r="F1234" s="1"/>
-      <c r="G1234" s="1"/>
-      <c r="H1234" s="1"/>
+      <c r="A1234" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1234" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1234" s="2">
+        <v>10115589</v>
+      </c>
+      <c r="D1234" s="2">
+        <v>6126801</v>
+      </c>
+      <c r="E1234" s="5">
+        <v>46143.416666666664</v>
+      </c>
+      <c r="F1234" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1234" s="2">
+        <v>37</v>
+      </c>
+      <c r="H1234" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="1235" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1235" s="1"/>
-      <c r="C1235" s="1"/>
-      <c r="D1235" s="1"/>
-      <c r="E1235" s="1"/>
-      <c r="F1235" s="1"/>
-      <c r="G1235" s="1"/>
-      <c r="H1235" s="1"/>
+      <c r="A1235" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1235" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1235" s="2">
+        <v>10117872</v>
+      </c>
+      <c r="D1235" s="2">
+        <v>6227119</v>
+      </c>
+      <c r="E1235" s="5">
+        <v>46144.416666666664</v>
+      </c>
+      <c r="F1235" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1235" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1235" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1236" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1236" s="1"/>
-      <c r="C1236" s="1"/>
-      <c r="D1236" s="1"/>
-      <c r="E1236" s="1"/>
-      <c r="F1236" s="1"/>
-      <c r="G1236" s="1"/>
-      <c r="H1236" s="1"/>
+      <c r="A1236" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1236" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1236" s="2">
+        <v>10119725</v>
+      </c>
+      <c r="D1236" s="2">
+        <v>5317029</v>
+      </c>
+      <c r="E1236" s="5">
+        <v>46146.916666666664</v>
+      </c>
+      <c r="F1236" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1236" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1236" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1237" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1237" s="1"/>
-      <c r="C1237" s="1"/>
-      <c r="D1237" s="1"/>
-      <c r="E1237" s="1"/>
-      <c r="F1237" s="1"/>
-      <c r="G1237" s="1"/>
-      <c r="H1237" s="1"/>
+      <c r="A1237" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1237" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1237" s="2">
+        <v>10128134</v>
+      </c>
+      <c r="D1237" s="2">
+        <v>6973319</v>
+      </c>
+      <c r="E1237" s="5">
+        <v>46148.416666666664</v>
+      </c>
+      <c r="F1237" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1237" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1237" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1238" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1238" s="1"/>
-      <c r="C1238" s="1"/>
-      <c r="D1238" s="1"/>
-      <c r="E1238" s="1"/>
-      <c r="F1238" s="1"/>
-      <c r="G1238" s="1"/>
-      <c r="H1238" s="1"/>
+      <c r="A1238" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1238" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1238" s="2">
+        <v>10136208</v>
+      </c>
+      <c r="D1238" s="2">
+        <v>4183662</v>
+      </c>
+      <c r="E1238" s="5">
+        <v>46151.416666666664</v>
+      </c>
+      <c r="F1238" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1238" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1238" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="1239" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1239" s="1"/>
-      <c r="C1239" s="1"/>
-      <c r="D1239" s="1"/>
-      <c r="E1239" s="1"/>
-      <c r="F1239" s="1"/>
-      <c r="G1239" s="1"/>
-      <c r="H1239" s="1"/>
+      <c r="A1239" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1239" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1239" s="2">
+        <v>10139326</v>
+      </c>
+      <c r="D1239" s="2">
+        <v>7292190</v>
+      </c>
+      <c r="E1239" s="5">
+        <v>46152.916666666664</v>
+      </c>
+      <c r="F1239" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1239" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1239" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1240" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1240" s="1"/>
-      <c r="C1240" s="1"/>
-      <c r="D1240" s="1"/>
-      <c r="E1240" s="1"/>
-      <c r="F1240" s="1"/>
-      <c r="G1240" s="1"/>
-      <c r="H1240" s="1"/>
+      <c r="A1240" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1240" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1240" s="2">
+        <v>10145495</v>
+      </c>
+      <c r="D1240" s="2">
+        <v>5317184</v>
+      </c>
+      <c r="E1240" s="5">
+        <v>46155.416666666664</v>
+      </c>
+      <c r="F1240" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1240" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1240" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1241" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1241" s="1"/>
-      <c r="C1241" s="1"/>
-      <c r="D1241" s="1"/>
-      <c r="E1241" s="1"/>
-      <c r="F1241" s="1"/>
-      <c r="G1241" s="1"/>
-      <c r="H1241" s="1"/>
+      <c r="A1241" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1241" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1241" s="2">
+        <v>9956746</v>
+      </c>
+      <c r="D1241" s="2">
+        <v>3570964</v>
+      </c>
+      <c r="E1241" s="5">
+        <v>46155.916666666664</v>
+      </c>
+      <c r="F1241" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1241" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1241" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="1242" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1242" s="1"/>
-      <c r="C1242" s="1"/>
-      <c r="D1242" s="1"/>
-      <c r="E1242" s="1"/>
-      <c r="F1242" s="1"/>
-      <c r="G1242" s="1"/>
-      <c r="H1242" s="1"/>
+      <c r="A1242" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1242" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1242" s="2">
+        <v>10149822</v>
+      </c>
+      <c r="D1242" s="2">
+        <v>7086066</v>
+      </c>
+      <c r="E1242" s="5">
+        <v>46157.916666666664</v>
+      </c>
+      <c r="F1242" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1242" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1242" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1243" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1243" s="1"/>
-      <c r="C1243" s="1"/>
-      <c r="D1243" s="1"/>
-      <c r="E1243" s="1"/>
-      <c r="F1243" s="1"/>
-      <c r="G1243" s="1"/>
-      <c r="H1243" s="1"/>
+      <c r="A1243" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1243" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1243" s="2">
+        <v>10157668</v>
+      </c>
+      <c r="D1243" s="2">
+        <v>4759102</v>
+      </c>
+      <c r="E1243" s="5">
+        <v>46161.416666666664</v>
+      </c>
+      <c r="F1243" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1243" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1243" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1244" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1244" s="1"/>
-      <c r="C1244" s="1"/>
-      <c r="D1244" s="1"/>
-      <c r="E1244" s="1"/>
-      <c r="F1244" s="1"/>
-      <c r="G1244" s="1"/>
-      <c r="H1244" s="1"/>
+      <c r="A1244" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1244" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1244" s="2">
+        <v>10165317</v>
+      </c>
+      <c r="D1244" s="2">
+        <v>7996920</v>
+      </c>
+      <c r="E1244" s="5">
+        <v>46163.416666666664</v>
+      </c>
+      <c r="F1244" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1244" s="2">
+        <v>22</v>
+      </c>
+      <c r="H1244" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1245" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1245" s="1"/>
-      <c r="C1245" s="1"/>
-      <c r="D1245" s="1"/>
-      <c r="E1245" s="1"/>
-      <c r="F1245" s="1"/>
-      <c r="G1245" s="1"/>
-      <c r="H1245" s="1"/>
+      <c r="A1245" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1245" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1245" s="2">
+        <v>10167877</v>
+      </c>
+      <c r="D1245" s="2">
+        <v>7999197</v>
+      </c>
+      <c r="E1245" s="5">
+        <v>46164.416666666664</v>
+      </c>
+      <c r="F1245" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1245" s="2">
+        <v>48</v>
+      </c>
+      <c r="H1245" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1246" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1246" s="1"/>
-      <c r="C1246" s="1"/>
-      <c r="D1246" s="1"/>
-      <c r="E1246" s="1"/>
-      <c r="F1246" s="1"/>
-      <c r="G1246" s="1"/>
-      <c r="H1246" s="1"/>
+      <c r="A1246" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1246" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1246" s="2">
+        <v>10168739</v>
+      </c>
+      <c r="D1246" s="2">
+        <v>8000161</v>
+      </c>
+      <c r="E1246" s="5">
+        <v>46164.916666666664</v>
+      </c>
+      <c r="F1246" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1246" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1246" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="1247" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1247" s="1"/>
-      <c r="C1247" s="1"/>
-      <c r="D1247" s="1"/>
-      <c r="E1247" s="1"/>
-      <c r="F1247" s="1"/>
-      <c r="G1247" s="1"/>
-      <c r="H1247" s="1"/>
+      <c r="A1247" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1247" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1247" s="2">
+        <v>10039587</v>
+      </c>
+      <c r="D1247" s="2">
+        <v>3570964</v>
+      </c>
+      <c r="E1247" s="5">
+        <v>46171.916666666664</v>
+      </c>
+      <c r="F1247" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1247" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1247" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="1248" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1248" s="1"/>
-      <c r="C1248" s="1"/>
-      <c r="D1248" s="1"/>
-      <c r="E1248" s="1"/>
-      <c r="F1248" s="1"/>
-      <c r="G1248" s="1"/>
-      <c r="H1248" s="1"/>
+      <c r="A1248" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1248" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1248" s="2">
+        <v>10189076</v>
+      </c>
+      <c r="D1248" s="2">
+        <v>4740911</v>
+      </c>
+      <c r="E1248" s="5">
+        <v>46172.916666666664</v>
+      </c>
+      <c r="F1248" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1248" s="2">
+        <v>72</v>
+      </c>
+      <c r="H1248" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1249" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1249" s="1"/>
-      <c r="C1249" s="1"/>
-      <c r="D1249" s="1"/>
-      <c r="E1249" s="1"/>
-      <c r="F1249" s="1"/>
-      <c r="G1249" s="1"/>
-      <c r="H1249" s="1"/>
+      <c r="A1249" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1249" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1249" s="2">
+        <v>10187189</v>
+      </c>
+      <c r="D1249" s="2">
+        <v>7086066</v>
+      </c>
+      <c r="E1249" s="5">
+        <v>46173.416666666664</v>
+      </c>
+      <c r="F1249" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1249" s="2">
+        <v>36</v>
+      </c>
+      <c r="H1249" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1250" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1250" s="1"/>
@@ -32953,51 +35335,6 @@
       <c r="G1453" s="1"/>
       <c r="H1453" s="1"/>
     </row>
-    <row r="1454" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1454" s="1"/>
-      <c r="C1454" s="1"/>
-      <c r="D1454" s="1"/>
-      <c r="E1454" s="1"/>
-      <c r="F1454" s="1"/>
-      <c r="G1454" s="1"/>
-      <c r="H1454" s="1"/>
-    </row>
-    <row r="1455" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1455" s="1"/>
-      <c r="C1455" s="1"/>
-      <c r="D1455" s="1"/>
-      <c r="E1455" s="1"/>
-      <c r="F1455" s="1"/>
-      <c r="G1455" s="1"/>
-      <c r="H1455" s="1"/>
-    </row>
-    <row r="1456" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1456" s="1"/>
-      <c r="C1456" s="1"/>
-      <c r="D1456" s="1"/>
-      <c r="E1456" s="1"/>
-      <c r="F1456" s="1"/>
-      <c r="G1456" s="1"/>
-      <c r="H1456" s="1"/>
-    </row>
-    <row r="1457" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1457" s="1"/>
-      <c r="C1457" s="1"/>
-      <c r="D1457" s="1"/>
-      <c r="E1457" s="1"/>
-      <c r="F1457" s="1"/>
-      <c r="G1457" s="1"/>
-      <c r="H1457" s="1"/>
-    </row>
-    <row r="1458" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A1458" s="1"/>
-      <c r="C1458" s="1"/>
-      <c r="D1458" s="1"/>
-      <c r="E1458" s="1"/>
-      <c r="F1458" s="1"/>
-      <c r="G1458" s="1"/>
-      <c r="H1458" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tønsberg.xls.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tønsberg.xls.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{C2EE9B90-B8AF-4771-9225-A9DAC15702B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F84B01A-5B3B-4166-BBA8-9E481D44B695}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{C2EE9B90-B8AF-4771-9225-A9DAC15702B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2DD1C2-5D56-4BDF-ABE4-195DA6829A94}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B856B024-48C7-4BFF-B5E4-3C408E652A68}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B856B024-48C7-4BFF-B5E4-3C408E652A68}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ark1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tønsberg" sheetId="1" r:id="rId1"/>
+    <sheet name="Sandefjord" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35338,4 +35339,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B68DFA-05BC-45CC-8C1C-DE5424B1FEDF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>